--- a/hhnk_threedi_tools/breaches/start_download_simulation/simulations_id.xlsx
+++ b/hhnk_threedi_tools/breaches/start_download_simulation/simulations_id.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\jacostabarragan\hhnk-threedi-tools\hhnk_threedi_tools\breaches\start_download_simulation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDEE6690-18FA-4459-9174-E308568E5A97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DEDA11-B1C0-4334-B81B-7E1882BDD6CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>scenario_name</t>
   </si>
@@ -41,6 +41,24 @@
   </si>
   <si>
     <t>SIZE_KB</t>
+  </si>
+  <si>
+    <t>date_simulation_created</t>
+  </si>
+  <si>
+    <t>date_simulation_downloaded</t>
+  </si>
+  <si>
+    <t>date_ldo_uploaded</t>
+  </si>
+  <si>
+    <t>schematitation_id</t>
+  </si>
+  <si>
+    <t>revision_number</t>
+  </si>
+  <si>
+    <t>model_id</t>
   </si>
 </sst>
 </file>
@@ -403,10 +421,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="20.5703125" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -414,18 +438,36 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
